--- a/outputs/qc/qc_group_stats.xlsx
+++ b/outputs/qc/qc_group_stats.xlsx
@@ -465,19 +465,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1276</v>
+        <v>1379</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02236459996067899</v>
+        <v>0.02889662559708631</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0164871590304688</v>
+        <v>0.0168724279835391</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06244395005518765</v>
+        <v>0.08699449401936581</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08705145243971898</v>
+        <v>0.2174303992303991</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1034</v>
+        <v>1081</v>
       </c>
       <c r="D3" t="n">
-        <v>0.058021885693361</v>
+        <v>0.06773895290432137</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0439737674100658</v>
+        <v>0.044954128440367</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1642334331778855</v>
+        <v>0.194130925507901</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2221241763031719</v>
+        <v>0.4195251661918343</v>
       </c>
     </row>
     <row r="4">
@@ -519,19 +519,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>937</v>
+        <v>1020</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01630214555177411</v>
+        <v>0.02527699547496693</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0113559322033898</v>
+        <v>0.01233047497415315</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04868569772496731</v>
+        <v>0.08809450353170409</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07072965606748866</v>
+        <v>0.2357681818181804</v>
       </c>
     </row>
     <row r="5">
@@ -546,19 +546,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>477</v>
+        <v>501</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03389648642657094</v>
+        <v>0.04774637232990089</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0259375</v>
+        <v>0.0271276595744681</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09419212973567269</v>
+        <v>0.143589743589744</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1281183304125476</v>
+        <v>0.430508474576271</v>
       </c>
     </row>
     <row r="6">
@@ -569,23 +569,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>alkaline</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>349</v>
+        <v>398</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01006786335368584</v>
+        <v>0.04920473445123454</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00666666666666667</v>
+        <v>0.01484831354814395</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03209103840682785</v>
+        <v>0.2382618356611647</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04114805065255338</v>
+        <v>0.4256215827183564</v>
       </c>
     </row>
     <row r="7">
@@ -596,23 +596,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>alkaline</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>331</v>
+        <v>383</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02422253972750863</v>
+        <v>0.01677183259432211</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0126984126984127</v>
+        <v>0.00723577235772358</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08670424754249026</v>
+        <v>0.05521901263427389</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1059827161028777</v>
+        <v>0.1522568756439727</v>
       </c>
     </row>
     <row r="8">
@@ -627,19 +627,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02819425679285035</v>
+        <v>0.03776396597212247</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0219285714285714</v>
+        <v>0.02275687684527465</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08110311600550622</v>
+        <v>0.1241114982578395</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1160152332292551</v>
+        <v>0.2667142312510218</v>
       </c>
     </row>
     <row r="9">
@@ -654,19 +654,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04236806064031666</v>
+        <v>0.09929704735896927</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0279569892473118</v>
+        <v>0.0331914893617021</v>
       </c>
       <c r="F9" t="n">
-        <v>0.139</v>
+        <v>0.3790585287274023</v>
       </c>
       <c r="G9" t="n">
-        <v>0.191044776119403</v>
+        <v>0.7858769230769235</v>
       </c>
     </row>
   </sheetData>
